--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -47,7 +47,7 @@
     <t>序号</t>
   </si>
   <si>
-    <t>随机数据</t>
+    <t>随机数据-CreatureModelInfo</t>
   </si>
   <si>
     <t>备注</t>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>角色创建-兽人</t>
+  </si>
+  <si>
+    <t>1030001-1030012,1040001-1040002,1050001-1050014,1060001-1060006</t>
   </si>
   <si>
     <t>人类-通用</t>
@@ -1204,10 +1207,10 @@
         <v>1000001</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -1218,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -1229,7 +1232,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -1240,7 +1243,7 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -1251,7 +1254,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -1262,7 +1265,7 @@
         <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1273,7 +1276,7 @@
         <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" ht="12" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
@@ -1,33 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="CreatureRandomInfo" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>id</t>
   </si>
@@ -53,7 +39,7 @@
     <t>备注</t>
   </si>
   <si>
-    <t>1030001-1030003,1040001-1040002,1050001-1050011,1060001-1060005</t>
+    <t>1030001-1030012,1040001-1040002,1050001-1050014,1060001-1060006</t>
   </si>
   <si>
     <t>角色创建-人类</t>
@@ -65,7 +51,7 @@
     <t>角色创建-骷髅</t>
   </si>
   <si>
-    <t>3040000-3040010,3050001-3050010,</t>
+    <t>3040001,3050001-3050010</t>
   </si>
   <si>
     <t>角色创建-史莱姆</t>
@@ -93,9 +79,6 @@
   </si>
   <si>
     <t>角色创建-兽人</t>
-  </si>
-  <si>
-    <t>1030001-1030012,1040001-1040002,1050001-1050014,1060001-1060006</t>
   </si>
   <si>
     <t>人类-通用</t>
@@ -122,19 +105,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -142,7 +119,6 @@
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -150,14 +126,12 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -165,7 +139,6 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -173,7 +146,6 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -181,7 +153,6 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -189,7 +160,6 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -197,14 +167,12 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -212,7 +180,6 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,7 +187,6 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -228,14 +194,12 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -243,42 +207,36 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -587,155 +545,303 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="51">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="3" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="4" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="5" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="7" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="8" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="9" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="10" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="5" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="11" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="6" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="12" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="7" applyFont="1" fillId="0" applyFill="1" borderId="2" applyBorder="1" xfId="13" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="3" applyBorder="1" xfId="14" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="15" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="9" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" xfId="16" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="10" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" xfId="17" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="11" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" xfId="18" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="12" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" xfId="19" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="13" applyFont="1" fillId="0" applyFill="1" borderId="7" applyBorder="1" xfId="20" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="14" applyFont="1" fillId="0" applyFill="1" borderId="8" applyBorder="1" xfId="21" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="1" xfId="22" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="1" xfId="23" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="17" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="1" xfId="24" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="1" xfId="25" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="1" xfId="26" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="1" xfId="27" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="1" xfId="28" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="1" xfId="29" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="1" xfId="30" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="1" xfId="31" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="1" xfId="32" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="1" xfId="33" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="1" xfId="34" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="1" xfId="35" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="1" xfId="36" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="1" xfId="37" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="1" xfId="38" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="1" xfId="39" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="1" xfId="40" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="1" xfId="41" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="1" xfId="42" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="1" xfId="43" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="1" xfId="44" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="1" xfId="45" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="1" xfId="46" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="19" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="1" xfId="47" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="18" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="1" xfId="48" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -789,11 +895,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1082,218 +1251,218 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.375"/>
-    <col min="2" max="2" width="88.25" customWidth="1"/>
-    <col min="3" max="3" width="42.875" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1" style="50"/>
+    <col min="2" max="2" width="88.25" customWidth="1" style="50"/>
+    <col min="3" max="3" width="42.875" customWidth="1" style="50"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="2">
+      <c r="A2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="50" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="50" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:3">
-      <c r="A4">
+    <row r="4" s="50" customFormat="1">
+      <c r="A4" s="50">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="50" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:3">
-      <c r="A5">
+    <row r="5" s="50" customFormat="1">
+      <c r="A5" s="50">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="50" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:3">
-      <c r="A6">
+    <row r="6" s="50" customFormat="1">
+      <c r="A6" s="50">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="50" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:3">
-      <c r="A7">
+    <row r="7" s="50" customFormat="1">
+      <c r="A7" s="50">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="50" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:3">
-      <c r="A8">
+    <row r="8" s="50" customFormat="1">
+      <c r="A8" s="50">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="50" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:3">
-      <c r="A9">
+    <row r="9" s="50" customFormat="1">
+      <c r="A9" s="50">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="50" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:3">
-      <c r="A10">
+    <row r="10" s="50" customFormat="1">
+      <c r="A10" s="50">
         <v>7</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="50" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:3">
-      <c r="A11">
+    <row r="11" s="50" customFormat="1">
+      <c r="A11" s="50">
         <v>1000001</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="50">
+        <v>2000001</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12">
-        <v>2000001</v>
-      </c>
-      <c r="B12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" t="s">
+    <row r="13">
+      <c r="A13" s="50">
+        <v>3000001</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="50" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13">
-        <v>3000001</v>
-      </c>
-      <c r="B13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
+    <row r="14">
+      <c r="A14" s="50">
+        <v>4000001</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="50" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14">
-        <v>4000001</v>
-      </c>
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" t="s">
+    <row r="15">
+      <c r="A15" s="50">
+        <v>5000001</v>
+      </c>
+      <c r="B15" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="50" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15">
-        <v>5000001</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
+    <row r="16">
+      <c r="A16" s="50">
+        <v>6000001</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="50" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16">
-        <v>6000001</v>
-      </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="17">
+      <c r="A17" s="50">
+        <v>7000001</v>
+      </c>
+      <c r="B17" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="50" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>7000001</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" ht="12" customHeight="1"/>
-    <row r="40" ht="12" customHeight="1"/>
-    <row r="41" ht="12" customHeight="1"/>
-    <row r="42" ht="12" customHeight="1"/>
-    <row r="43" ht="12" customHeight="1"/>
-    <row r="44" ht="12" customHeight="1"/>
-    <row r="45" ht="12" customHeight="1"/>
-    <row r="46" ht="12" customHeight="1"/>
-    <row r="47" ht="12" customHeight="1"/>
+    <row r="39" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="40" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="41" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="42" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="43" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="44" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="45" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="46" ht="12" customHeight="1" s="50" customFormat="1"/>
+    <row r="47" ht="12" customHeight="1" s="50" customFormat="1"/>
   </sheetData>
-  <sortState ref="A4:I88">
-    <sortCondition ref="A4"/>
-  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
@@ -1165,7 +1165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" style="50" min="1" max="1"/>
@@ -1174,461 +1174,587 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>random_type</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="49" t="inlineStr">
         <is>
           <t>skin_random_data</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>equip_random_data</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>随机类型（0=皮肤池 1=装备池）</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
+        <is>
+          <t>随机类型（0=皮肤池 1=装备池 2=套装池）</t>
+        </is>
+      </c>
+      <c r="C3" s="49" t="inlineStr">
         <is>
           <t>随机数据-CreatureModelInfo</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>装备随机数据-ItemsInfo（装备道具ID池，区间压缩串，同skin_random_data格式）</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="49" t="inlineStr">
+        <is>
+          <t>装备/套装随机数据（type=1时为ItemsInfo道具ID池，type=2时为EquipSuitInfo套装ID池；区间压缩串，同skin_random_data格式）</t>
+        </is>
+      </c>
+      <c r="E3" s="49" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4" s="50">
-      <c r="A4" t="n">
+      <c r="A4" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>1030001-1030012,1040001-1040002,1050001-1050014,1060001-1060006</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>角色创建-人类</t>
         </is>
       </c>
     </row>
     <row r="5" s="50">
-      <c r="A5" t="n">
+      <c r="A5" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="49" t="inlineStr">
         <is>
           <t>2010000-2010013</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="49" t="inlineStr">
         <is>
           <t>角色创建-骷髅</t>
         </is>
       </c>
     </row>
     <row r="6" s="50">
-      <c r="A6" t="n">
+      <c r="A6" s="49" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="49" t="inlineStr">
         <is>
           <t>3040001,3050001-3050010</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="49" t="inlineStr">
         <is>
           <t>角色创建-史莱姆</t>
         </is>
       </c>
     </row>
     <row r="7" s="50">
-      <c r="A7" t="n">
+      <c r="A7" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="49" t="inlineStr">
         <is>
           <t>4030001-4030010,4050001-4050010,4060001-4060010,4070001-4070010,4080001-4080004</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="49" t="inlineStr">
         <is>
           <t>角色创建-魅魔</t>
         </is>
       </c>
     </row>
     <row r="8" s="50">
-      <c r="A8" t="n">
+      <c r="A8" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="49" t="inlineStr">
         <is>
           <t>5050001-5050011,5070001-5070005</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="49" t="inlineStr">
         <is>
           <t>角色创建-牛头人</t>
         </is>
       </c>
     </row>
     <row r="9" s="50">
-      <c r="A9" t="n">
+      <c r="A9" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="49" t="inlineStr">
         <is>
           <t>6050001-6050010,6060001-6060010</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="49" t="inlineStr">
         <is>
           <t>角色创建-哥布林</t>
         </is>
       </c>
     </row>
     <row r="10" s="50">
-      <c r="A10" t="n">
+      <c r="A10" s="49" t="n">
         <v>7</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>7030001-7030002,7050001-7050005,7060001-7060005</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>角色创建-兽人</t>
         </is>
       </c>
     </row>
     <row r="11" s="50">
-      <c r="A11" t="n">
+      <c r="A11" s="49" t="n">
         <v>1000001</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>1030001-1030012,1040001-1040002,1050001-1050014,1060001-1060006</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>人类-通用</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="49" t="n">
         <v>2000001</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="49" t="inlineStr">
         <is>
           <t>2010000-2010013</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="49" t="inlineStr">
         <is>
           <t>骷髅-通用</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="49" t="n">
         <v>3000001</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="49" t="inlineStr">
         <is>
           <t>3040001,3050001-3050010</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="49" t="inlineStr">
         <is>
           <t>史莱姆-通用</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="49" t="n">
         <v>4000001</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="49" t="inlineStr">
         <is>
           <t>4030001-4030010,4050001-4050010,4060001-4060010,4070001-4070010,4080001-4080004</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="49" t="inlineStr">
         <is>
           <t>魅魔-通用</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="49" t="n">
         <v>5000001</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="49" t="inlineStr">
         <is>
           <t>5050001-5050011,5070001-5070005</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="49" t="inlineStr">
         <is>
           <t>牛头人-通用</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="49" t="n">
         <v>6000001</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="49" t="inlineStr">
         <is>
           <t>6050001-6050010,6060001-6060010</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="49" t="inlineStr">
         <is>
           <t>哥布林-通用</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="49" t="n">
         <v>7000001</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="49" t="inlineStr">
         <is>
           <t>7030001-7030002,7050001-7050005,7060001-7060005</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="49" t="inlineStr">
         <is>
           <t>兽人-通用</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="49" t="n">
         <v>10000001</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="49" t="inlineStr">
         <is>
           <t>10100001-10100005,10100007-10100008,10100010,10100012-10100017,10200001-10200017,10300001-10300017,11000001-11000013,11010001-11010003,11020021-11020022</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="49" t="inlineStr">
         <is>
           <t>装备池-人类</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="49" t="n">
         <v>20000001</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="49" t="inlineStr">
         <is>
           <t>20100001-20100007,20200001-20200011,20300001,20300003,20300007,20300009,20300011,21000001-21000010,21010001-21010020</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="49" t="inlineStr">
         <is>
           <t>装备池-骷髅</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="49" t="n">
         <v>30000001</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>30100001-30100020</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="49" t="inlineStr">
         <is>
           <t>装备池-史莱姆</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="49" t="n">
         <v>40000001</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="49" t="inlineStr">
         <is>
           <t>40100001,40200001-40200006,40300001-40300004,41000001-41000005</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="49" t="inlineStr">
         <is>
           <t>装备池-魅魔</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="49" t="n">
         <v>50000001</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="49" t="inlineStr">
         <is>
           <t>50100001-50100003,50200001-50200003,50300001-50300002,50500001-50500005,51010001-51010003</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="49" t="inlineStr">
         <is>
           <t>装备池-牛头人</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="49" t="n">
         <v>60000001</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="49" t="inlineStr">
         <is>
           <t>60100001-60100010,60200001-60200002,60300001-60300005,61010001-61010020</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="49" t="inlineStr">
         <is>
           <t>装备池-哥布林</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="49" t="n">
         <v>70000001</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="49" t="inlineStr">
         <is>
           <t>70100001,70200001-70200002,70300001-70300004,71000001-71000003,71010001-71010006</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="49" t="inlineStr">
         <is>
           <t>装备池-兽人</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="49" t="n">
+        <v>20000002</v>
+      </c>
+      <c r="B25" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="49" t="inlineStr">
+        <is>
+          <t>200001-200008</t>
+        </is>
+      </c>
+      <c r="E25" s="49" t="inlineStr">
+        <is>
+          <t>套装池-骷髅</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>10000002</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>100001</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>套装池-人类</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>30000002</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>300001,300002</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>套装池-史莱姆</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>40000002</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>400001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>套装池-魅魔</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>50000002</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>500001</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>套装池-牛头人</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>60000002</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>600001</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>套装池-哥布林</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>70000002</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>700001</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>套装池-兽人</t>
         </is>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_creature_random_info[生物随机信息] .xlsx
@@ -1641,7 +1641,7 @@
       </c>
       <c r="D25" s="49" t="inlineStr">
         <is>
-          <t>200001-200008</t>
+          <t>200001-200011</t>
         </is>
       </c>
       <c r="E25" s="49" t="inlineStr">
@@ -1651,108 +1651,108 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="49" t="n">
         <v>10000002</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>100001</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D26" s="49" t="inlineStr">
+        <is>
+          <t>100001-100017</t>
+        </is>
+      </c>
+      <c r="E26" s="49" t="inlineStr">
         <is>
           <t>套装池-人类</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="49" t="n">
         <v>30000002</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>300001,300002</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>300001-300020</t>
+        </is>
+      </c>
+      <c r="E27" s="49" t="inlineStr">
         <is>
           <t>套装池-史莱姆</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="49" t="n">
         <v>40000002</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>400001</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="D28" s="49" t="inlineStr">
+        <is>
+          <t>400001-400006</t>
+        </is>
+      </c>
+      <c r="E28" s="49" t="inlineStr">
         <is>
           <t>套装池-魅魔</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="49" t="n">
         <v>50000002</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>500001</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="D29" s="49" t="inlineStr">
+        <is>
+          <t>500001-500003</t>
+        </is>
+      </c>
+      <c r="E29" s="49" t="inlineStr">
         <is>
           <t>套装池-牛头人</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="49" t="n">
         <v>60000002</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>600001</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D30" s="49" t="inlineStr">
+        <is>
+          <t>600001-600002</t>
+        </is>
+      </c>
+      <c r="E30" s="49" t="inlineStr">
         <is>
           <t>套装池-哥布林</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="49" t="n">
         <v>70000002</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="49" t="n">
         <v>2</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>700001</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="49" t="inlineStr">
+        <is>
+          <t>700001-700002</t>
+        </is>
+      </c>
+      <c r="E31" s="49" t="inlineStr">
         <is>
           <t>套装池-兽人</t>
         </is>
